--- a/pipeline_output/PB_CH_2W_H&M.xlsx
+++ b/pipeline_output/PB_CH_2W_H&M.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.5</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -7327,12 +7327,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7815,12 +7815,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8557,12 +8557,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -8684,12 +8684,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8811,12 +8811,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -8928,12 +8928,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -9045,12 +9045,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9533,12 +9533,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -10021,12 +10021,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10372,12 +10372,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10489,12 +10489,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10743,12 +10743,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10860,12 +10860,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -11094,12 +11094,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -11562,12 +11562,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -11689,12 +11689,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -12187,12 +12187,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -12538,12 +12538,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -12772,12 +12772,12 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -12899,12 +12899,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -13026,12 +13026,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -13270,12 +13270,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -13524,12 +13524,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -13651,12 +13651,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -14012,12 +14012,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -14191,7 +14191,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -14383,12 +14383,12 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -14510,12 +14510,12 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -14637,12 +14637,12 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -14754,12 +14754,12 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -14871,12 +14871,12 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -15050,7 +15050,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -15167,7 +15167,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -15222,12 +15222,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -15476,12 +15476,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -15538,7 +15538,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -15603,12 +15603,12 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -15665,7 +15665,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -15730,12 +15730,12 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -15847,12 +15847,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -15974,12 +15974,12 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -16101,12 +16101,12 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -16218,12 +16218,12 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -16280,7 +16280,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -16345,12 +16345,12 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -16407,7 +16407,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -16472,12 +16472,12 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -16589,12 +16589,12 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -16716,12 +16716,12 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -16778,7 +16778,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, HARYANA, PUNJAB</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -16843,12 +16843,12 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -17087,12 +17087,12 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -17214,12 +17214,12 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -17341,12 +17341,12 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -17468,12 +17468,12 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -17585,12 +17585,12 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -17702,12 +17702,12 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -17722,7 +17722,7 @@
       </c>
       <c r="AQ140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -17819,12 +17819,12 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -17936,12 +17936,12 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -18053,12 +18053,12 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -18180,12 +18180,12 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -18307,12 +18307,12 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -18434,12 +18434,12 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -18561,12 +18561,12 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -18678,12 +18678,12 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -18805,12 +18805,12 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -18932,12 +18932,12 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -19049,12 +19049,12 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -19176,12 +19176,12 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -19303,12 +19303,12 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -19420,12 +19420,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -19547,12 +19547,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -19791,12 +19791,12 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -19918,12 +19918,12 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -20045,12 +20045,12 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -20172,12 +20172,12 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -20299,12 +20299,12 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -20416,12 +20416,12 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -20533,12 +20533,12 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -20650,12 +20650,12 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -20884,12 +20884,12 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -21011,12 +21011,12 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -21138,12 +21138,12 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -21265,12 +21265,12 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -21392,12 +21392,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -21509,12 +21509,12 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -21763,12 +21763,12 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -21880,12 +21880,12 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -22007,12 +22007,12 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -22134,12 +22134,12 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -22251,12 +22251,12 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -22378,12 +22378,12 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -22505,12 +22505,12 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -22525,7 +22525,7 @@
       </c>
       <c r="AQ179" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -22567,7 +22567,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -22632,12 +22632,12 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -22759,12 +22759,12 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -22948,7 +22948,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -23013,12 +23013,12 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -23075,7 +23075,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -23140,12 +23140,12 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -23267,12 +23267,12 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -23329,7 +23329,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -23394,12 +23394,12 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -23456,7 +23456,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -23521,12 +23521,12 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
@@ -23583,7 +23583,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -23638,12 +23638,12 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
@@ -23700,7 +23700,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -23755,12 +23755,12 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
@@ -23817,7 +23817,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -23872,12 +23872,12 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -23989,12 +23989,12 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
@@ -24051,7 +24051,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -24106,12 +24106,12 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
@@ -24168,7 +24168,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -24223,12 +24223,12 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -24340,12 +24340,12 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
@@ -24402,7 +24402,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -24457,12 +24457,12 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN195" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
@@ -24519,7 +24519,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -24574,12 +24574,12 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN196" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
@@ -24636,7 +24636,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -24691,12 +24691,12 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
@@ -24753,7 +24753,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -24808,12 +24808,12 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
@@ -24870,7 +24870,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -24925,12 +24925,12 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
@@ -24987,7 +24987,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -25042,12 +25042,12 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
@@ -25104,7 +25104,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -25159,12 +25159,12 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
@@ -25221,7 +25221,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -25276,12 +25276,12 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
@@ -25338,7 +25338,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>CHANDIGARH</t>
+          <t>CHANDIGARH, PUNJAB</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -25393,12 +25393,12 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN203" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
